--- a/PICHINCHA/Diciembre/PICHINCHA-Diciembre.xlsx
+++ b/PICHINCHA/Diciembre/PICHINCHA-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2E99EB-180C-49A6-AF86-16F6DFBC0396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A2FE3-85B4-46FC-A921-0B65E0FEEF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="82">
   <si>
     <t>UF</t>
   </si>
@@ -205,9 +205,6 @@
     <t>PICHINCHA  267 - LANUS OESTE</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA</t>
-  </si>
-  <si>
     <t>GABRIEL</t>
   </si>
   <si>
@@ -253,25 +250,28 @@
     <t>TSG</t>
   </si>
   <si>
-    <t>Mes de OCTUBRE NO abonado</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Vto. 15/12</t>
-  </si>
-  <si>
-    <t>Liquidacion mes de NOVIEMBRE</t>
-  </si>
-  <si>
-    <t>NOVIEMBRE</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
     <t>Julio doartero - Reparacion de porton</t>
+  </si>
+  <si>
+    <t>Mes de octubre adeudado</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de DICIEMBRE</t>
+  </si>
+  <si>
+    <t>DICIEMBRE</t>
+  </si>
+  <si>
+    <t>Vto. 15/01</t>
+  </si>
+  <si>
+    <t>Prevision Ordinaria</t>
   </si>
 </sst>
 </file>
@@ -284,7 +284,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,13 +385,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1100,7 +1093,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1302,7 +1295,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1377,8 +1369,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1746,23 +1737,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1770,27 +1761,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1801,10 +1792,10 @@
         <v>78</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1812,29 +1803,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="125" t="s">
+      <c r="E11" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="125"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="124"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="149">
+      <c r="C12" s="121">
         <v>18252.89</v>
       </c>
       <c r="D12" s="5"/>
@@ -1842,28 +1833,28 @@
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <v>-514198.83977246739</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-279626.99777246732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="107" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="122">
+        <v>77</v>
+      </c>
+      <c r="C13" s="121">
         <v>0</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="124"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" s="122"/>
+      <c r="F13" s="123"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="121">
         <v>119977</v>
       </c>
       <c r="D14" s="43"/>
@@ -1872,10 +1863,10 @@
       </c>
       <c r="F14" s="59">
         <f>'prorrateo '!F10</f>
-        <v>937279.94200000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>713950.86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>19</v>
       </c>
@@ -1890,353 +1881,341 @@
         <v>20</v>
       </c>
       <c r="F15" s="59">
-        <f>-(C40)</f>
-        <v>-775108.74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-(C39)</f>
+        <v>-601015.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="108"/>
-      <c r="C16" s="148">
+      <c r="C16" s="119">
         <v>71368.7</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="58"/>
       <c r="F16" s="59"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="108"/>
-      <c r="C17" s="120">
-        <v>134601.26</v>
+      <c r="C17" s="119">
+        <v>118666.11</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="108"/>
-      <c r="C18" s="148">
-        <v>118666.11</v>
+        <v>71</v>
+      </c>
+      <c r="C18" s="119">
+        <v>56295.43</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="148">
-        <v>56295.43</v>
+        <v>73</v>
+      </c>
+      <c r="C19" s="119">
+        <v>15103</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="148">
-        <v>15103</v>
-      </c>
-      <c r="D20" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="C20" s="119">
+        <v>0</v>
+      </c>
       <c r="E20" s="58"/>
       <c r="F20" s="59"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="120">
-        <v>14341.6</v>
-      </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="59"/>
-      <c r="H21" s="108"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="87">
-        <f>SUM(C12:C21)</f>
-        <v>588605.99</v>
-      </c>
-      <c r="E22" s="60" t="s">
+      <c r="H20" s="108"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="87">
+        <f>SUM(C12:C20)</f>
+        <v>439663.13</v>
+      </c>
+      <c r="E21" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="119">
-        <f>SUM(F12:F21)</f>
-        <v>-352027.63777246734</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="34" t="s">
+      <c r="F21" s="147">
+        <f>SUM(F12:F20)</f>
+        <v>-166692.01777246734</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="113"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="119">
+        <v>71833</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B24" s="35"/>
-      <c r="C24" s="120">
-        <v>71833</v>
+      <c r="C24" s="119">
+        <v>4519.75</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B25" s="35"/>
-      <c r="C25" s="120">
-        <v>4519.75</v>
+      <c r="C25" s="119">
+        <v>0</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="120">
-        <v>25150</v>
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="126" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="127"/>
+      <c r="C26" s="119">
+        <v>85000</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="127" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="128"/>
-      <c r="C27" s="148">
-        <v>85000</v>
-      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="112"/>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="112"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="32"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="109">
+        <f>SUM(C22:C27)</f>
+        <v>161352.75</v>
+      </c>
       <c r="D28" s="5"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="109">
-        <f>SUM(C23:C28)</f>
-        <v>186502.75</v>
+      <c r="E28" s="5"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49">
+        <f>+C28+C21</f>
+        <v>601015.88</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="49">
-        <f>+C29+C22</f>
-        <v>775108.74</v>
-      </c>
-      <c r="D30" s="5"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="82"/>
+      <c r="C30" s="83"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="69" t="s">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="82"/>
-      <c r="C31" s="83"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="20"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="54"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="54"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="52"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="53">
+        <v>0</v>
+      </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="52"/>
-      <c r="B34" s="51"/>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="61"/>
+      <c r="B34" s="62"/>
       <c r="C34" s="53">
         <v>0</v>
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="53">
-        <v>0</v>
-      </c>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="78"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="81"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="78"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="81"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="86"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="78"/>
-      <c r="B37" s="85"/>
-      <c r="C37" s="86"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="81">
+        <v>0</v>
+      </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="78"/>
-      <c r="B38" s="84"/>
-      <c r="C38" s="81">
-        <v>0</v>
-      </c>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="63" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="65">
-        <f>SUM(C34:C38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B38" s="64"/>
+      <c r="C38" s="65">
+        <f>SUM(C33:C37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="53">
-        <f>C30-C28</f>
-        <v>775108.74</v>
+      <c r="C39" s="53">
+        <f>C29-C27</f>
+        <v>601015.88</v>
+      </c>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="77">
+        <f>+C29</f>
+        <v>601015.88</v>
       </c>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="77">
-        <f>+C30</f>
-        <v>775108.74</v>
-      </c>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="63" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="64"/>
-      <c r="C42" s="65">
-        <f>+C30+C39</f>
-        <v>775108.74</v>
-      </c>
-      <c r="E42" s="16"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="126"/>
-      <c r="C49" s="126"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="126"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="126"/>
-      <c r="C50" s="126"/>
-      <c r="D50" s="126"/>
-      <c r="E50" s="126"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="126"/>
-      <c r="C51" s="126"/>
-      <c r="D51" s="126"/>
-      <c r="E51" s="126"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="65">
+        <f>+C29+C38</f>
+        <v>601015.88</v>
+      </c>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="125"/>
+      <c r="C48" s="125"/>
+      <c r="D48" s="125"/>
+      <c r="E48" s="125"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="125"/>
+      <c r="C49" s="125"/>
+      <c r="D49" s="125"/>
+      <c r="E49" s="125"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="125"/>
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="19"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="20"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="18"/>
       <c r="B63" s="18"/>
-      <c r="C63" s="20"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C63" s="18"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="18"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B49:E51"/>
-    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="B48:E50"/>
+    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2254,25 +2233,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2280,7 +2259,7 @@
       <c r="C1" s="106"/>
       <c r="D1" s="26"/>
       <c r="E1" s="25"/>
-      <c r="F1" s="121"/>
+      <c r="F1" s="120"/>
       <c r="G1" s="25" t="s">
         <v>47</v>
       </c>
@@ -2288,15 +2267,15 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="71">
-        <v>702708.1</v>
+        <v>601015.88</v>
       </c>
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de NOVIEMBRE</v>
+        <v>Liquidacion mes de DICIEMBRE</v>
       </c>
       <c r="B2" s="73"/>
       <c r="C2" s="73"/>
@@ -2313,7 +2292,7 @@
       <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2348,13 +2327,13 @@
         <v>38</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2382,13 +2361,13 @@
       </c>
       <c r="L4" s="66" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 15/12</v>
+        <v>Vto. 15/01</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2396,14 +2375,15 @@
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="41">
-        <v>239940</v>
+        <v>146163</v>
       </c>
       <c r="F5" s="80">
-        <v>239940</v>
+        <f>E5</f>
+        <v>146163</v>
       </c>
       <c r="G5" s="67">
         <f>E5-F5</f>
@@ -2418,7 +2398,7 @@
       </c>
       <c r="J5" s="38">
         <f>K$1/5</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="K5" s="117">
         <f>K2*D5</f>
@@ -2426,14 +2406,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>146163.28479999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>125011.30304000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2441,30 +2421,30 @@
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="41">
-        <v>172120.31399999998</v>
+        <v>140541.62</v>
       </c>
       <c r="F6" s="80">
-        <f>E6</f>
-        <v>172120.31399999998</v>
+        <f t="shared" ref="F6:F9" si="0">E6</f>
+        <v>140541.62</v>
       </c>
       <c r="G6" s="67">
         <f>E6-F6</f>
         <v>0</v>
       </c>
       <c r="H6" s="70">
-        <f t="shared" ref="H6:H9" si="0">IF(G6&gt;0,G6*4%,0)</f>
+        <f t="shared" ref="H6:H9" si="1">IF(G6&gt;0,G6*4%,0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="38">
-        <f t="shared" ref="J6:J9" si="1">K$1/5</f>
-        <v>140541.62</v>
+        <f t="shared" ref="J6:J9" si="2">K$1/5</f>
+        <v>120203.17600000001</v>
       </c>
       <c r="K6" s="117">
         <f>K2*D6</f>
@@ -2472,14 +2452,14 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="M6" s="39">
-        <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>146163.28479999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M6:M9" si="3">L6*4%+L6</f>
+        <v>125011.30304000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2487,29 +2467,30 @@
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="41">
-        <v>180979</v>
+        <v>146163</v>
       </c>
       <c r="F7" s="80">
-        <v>180979</v>
+        <f t="shared" si="0"/>
+        <v>146163</v>
       </c>
       <c r="G7" s="67">
-        <f t="shared" ref="G7:G8" si="3">E7-F7</f>
+        <f t="shared" ref="G7:G8" si="4">E7-F7</f>
         <v>0</v>
       </c>
       <c r="H7" s="70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="38">
-        <f t="shared" si="1"/>
-        <v>140541.62</v>
+        <f t="shared" si="2"/>
+        <v>120203.17600000001</v>
       </c>
       <c r="K7" s="117">
         <f>K2*D7</f>
@@ -2517,14 +2498,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="M7" s="39">
-        <f t="shared" si="2"/>
-        <v>146163.28479999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>125011.30304000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2532,30 +2513,30 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
-        <v>172120.31399999998</v>
+        <v>140541.62</v>
       </c>
       <c r="F8" s="80">
-        <f>E8</f>
-        <v>172120.31399999998</v>
+        <f t="shared" si="0"/>
+        <v>140541.62</v>
       </c>
       <c r="G8" s="67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H8" s="70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="38">
-        <f t="shared" si="1"/>
-        <v>140541.62</v>
+        <f t="shared" si="2"/>
+        <v>120203.17600000001</v>
       </c>
       <c r="K8" s="117">
         <f>K2*D8</f>
@@ -2563,14 +2544,14 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="M8" s="39">
-        <f t="shared" si="2"/>
-        <v>146163.28479999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>125011.30304000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2578,30 +2559,30 @@
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="41">
-        <v>172120.31399999998</v>
+        <v>140541.62</v>
       </c>
       <c r="F9" s="80">
-        <f>E9</f>
-        <v>172120.31399999998</v>
+        <f t="shared" si="0"/>
+        <v>140541.62</v>
       </c>
       <c r="G9" s="67">
         <f>E9-F9</f>
         <v>0</v>
       </c>
       <c r="H9" s="70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
       </c>
       <c r="J9" s="38">
-        <f t="shared" si="1"/>
-        <v>140541.62</v>
+        <f t="shared" si="2"/>
+        <v>120203.17600000001</v>
       </c>
       <c r="K9" s="117">
         <f>K2*D9</f>
@@ -2609,125 +2590,125 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="M9" s="39">
-        <f t="shared" si="2"/>
-        <v>146163.28479999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>125011.30304000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="45">
-        <f t="shared" ref="D10:M10" si="4">SUM(D5:D9)</f>
+        <f t="shared" ref="D10:M10" si="5">SUM(D5:D9)</f>
         <v>0</v>
       </c>
       <c r="E10" s="42">
-        <f t="shared" si="4"/>
-        <v>937279.94200000004</v>
+        <f t="shared" si="5"/>
+        <v>713950.86</v>
       </c>
       <c r="F10" s="42">
         <f>SUM(F5:F9)</f>
-        <v>937279.94200000004</v>
+        <v>713950.86</v>
       </c>
       <c r="G10" s="50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H10" s="50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f t="shared" si="4"/>
-        <v>702708.1</v>
+        <f t="shared" si="5"/>
+        <v>601015.88</v>
       </c>
       <c r="K10" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L10" s="118">
-        <f t="shared" si="4"/>
-        <v>702708.1</v>
+        <f t="shared" si="5"/>
+        <v>601015.88</v>
       </c>
       <c r="M10" s="118">
-        <f t="shared" si="4"/>
-        <v>730816.424</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="129"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>625056.51520000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="128"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="129"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="129"/>
+      <c r="L15" s="129"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2743,68 +2724,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="136" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="139" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="140"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142">
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="141">
         <v>565</v>
       </c>
-      <c r="E2" s="143"/>
+      <c r="E2" s="142"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="144" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="131" t="s">
+      <c r="E3" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="131" t="s">
+      <c r="F3" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="131" t="s">
+      <c r="G3" s="130" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="145"/>
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="144"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -2827,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -2850,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -2873,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -2896,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -2919,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -2942,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -2961,12 +2942,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="135"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="132"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Diciembre/PICHINCHA-Diciembre.xlsx
+++ b/PICHINCHA/Diciembre/PICHINCHA-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A2FE3-85B4-46FC-A921-0B65E0FEEF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D046819-5855-4CD5-9C2D-E91A060B4565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1300,6 +1300,7 @@
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1369,7 +1370,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1738,22 +1738,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1761,27 +1761,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1803,24 +1803,24 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="124" t="s">
+      <c r="E11" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="124"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="125"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="107" t="s">
         <v>64</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>-279626.99777246732</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="107" t="s">
         <v>64</v>
       </c>
@@ -1850,7 +1850,7 @@
       <c r="E13" s="122"/>
       <c r="F13" s="123"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
         <v>45</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>713950.86</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
         <v>19</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>-601015.88</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
         <v>70</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="E16" s="58"/>
       <c r="F16" s="59"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
         <v>68</v>
       </c>
@@ -1909,7 +1909,7 @@
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
         <v>71</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="31" t="s">
         <v>73</v>
       </c>
@@ -1931,7 +1931,7 @@
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
         <v>69</v>
       </c>
@@ -1942,7 +1942,7 @@
       <c r="F20" s="59"/>
       <c r="H20" s="108"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="32"/>
       <c r="B21" s="33"/>
       <c r="C21" s="87">
@@ -1952,12 +1952,12 @@
       <c r="E21" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="147">
+      <c r="F21" s="124">
         <f>SUM(F12:F20)</f>
         <v>-166692.01777246734</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
         <v>21</v>
       </c>
@@ -1966,7 +1966,7 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
         <v>63</v>
       </c>
@@ -1978,7 +1978,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="31" t="s">
         <v>72</v>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
         <v>75</v>
       </c>
@@ -2002,11 +2002,11 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126" t="s">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="127"/>
+      <c r="B26" s="128"/>
       <c r="C26" s="119">
         <v>85000</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="31" t="s">
         <v>81</v>
       </c>
@@ -2024,7 +2024,7 @@
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="32"/>
       <c r="B28" s="33"/>
       <c r="C28" s="109">
@@ -2036,7 +2036,7 @@
       <c r="F28" s="55"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
         <v>12</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="69" t="s">
         <v>24</v>
       </c>
@@ -2058,18 +2058,18 @@
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="29"/>
       <c r="C32" s="54"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="52"/>
       <c r="B33" s="51"/>
       <c r="C33" s="53">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="61"/>
       <c r="B34" s="62"/>
       <c r="C34" s="53">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="78"/>
       <c r="B35" s="79"/>
       <c r="C35" s="81"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="78"/>
       <c r="B36" s="85"/>
       <c r="C36" s="86"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="78"/>
       <c r="B37" s="84"/>
       <c r="C37" s="81">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="63" t="s">
         <v>23</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>49</v>
       </c>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="63" t="s">
         <v>13</v>
       </c>
@@ -2146,67 +2146,67 @@
       </c>
       <c r="E41" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="125"/>
-      <c r="C48" s="125"/>
-      <c r="D48" s="125"/>
-      <c r="E48" s="125"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="125"/>
-      <c r="C49" s="125"/>
-      <c r="D49" s="125"/>
-      <c r="E49" s="125"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="125"/>
-      <c r="C50" s="125"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="125"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="126"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="126"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="126"/>
+      <c r="C49" s="126"/>
+      <c r="D49" s="126"/>
+      <c r="E49" s="126"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="126"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="19"/>
       <c r="B62" s="18"/>
       <c r="C62" s="20"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="18"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -2233,25 +2233,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2272,7 +2272,7 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de DICIEMBRE</v>
@@ -2292,7 +2292,7 @@
       <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2367,7 +2367,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>125011.30304000001</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>125011.30304000001</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>125011.30304000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>125011.30304000001</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>125011.30304000001</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2644,71 +2644,71 @@
         <v>625056.51520000002</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="128"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="128"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="129"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="129"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2724,68 +2724,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="135" t="s">
+    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="136" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="138" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="141">
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142">
         <v>565</v>
       </c>
-      <c r="E2" s="142"/>
+      <c r="E2" s="143"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="143" t="s">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="145" t="s">
+      <c r="D3" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="130" t="s">
+      <c r="E3" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="130" t="s">
+      <c r="F3" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="130" t="s">
+      <c r="G3" s="131" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="144"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="145"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -2942,12 +2942,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="134"/>
+    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Diciembre/PICHINCHA-Diciembre.xlsx
+++ b/PICHINCHA/Diciembre/PICHINCHA-Diciembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A2FE3-85B4-46FC-A921-0B65E0FEEF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17862406-BF04-4586-8A9D-14915A1EBDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1300,6 +1300,7 @@
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1369,7 +1370,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1815,10 +1815,10 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="124" t="s">
+      <c r="E11" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="124"/>
+      <c r="F11" s="125"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
@@ -1952,7 +1952,7 @@
       <c r="E21" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="147">
+      <c r="F21" s="124">
         <f>SUM(F12:F20)</f>
         <v>-166692.01777246734</v>
       </c>
@@ -2003,10 +2003,10 @@
       <c r="F25" s="20"/>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126" t="s">
+      <c r="A26" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="127"/>
+      <c r="B26" s="128"/>
       <c r="C26" s="119">
         <v>85000</v>
       </c>
@@ -2154,22 +2154,22 @@
       <c r="E47" s="16"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="125"/>
-      <c r="C48" s="125"/>
-      <c r="D48" s="125"/>
-      <c r="E48" s="125"/>
+      <c r="B48" s="126"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="126"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="125"/>
-      <c r="C49" s="125"/>
-      <c r="D49" s="125"/>
-      <c r="E49" s="125"/>
+      <c r="B49" s="126"/>
+      <c r="C49" s="126"/>
+      <c r="D49" s="126"/>
+      <c r="E49" s="126"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="125"/>
-      <c r="C50" s="125"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="125"/>
+      <c r="B50" s="126"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
@@ -2645,70 +2645,70 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="128"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="128"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="129"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="129"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2730,60 +2730,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="136" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="141">
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142">
         <v>565</v>
       </c>
-      <c r="E2" s="142"/>
+      <c r="E2" s="143"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="143" t="s">
+      <c r="A3" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="145" t="s">
+      <c r="D3" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="130" t="s">
+      <c r="E3" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="130" t="s">
+      <c r="F3" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="130" t="s">
+      <c r="G3" s="131" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="144"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
@@ -2943,11 +2943,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="134"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>
